--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126290096</v>
+        <v>126290817</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,39 +3341,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585620</v>
+        <v>585783</v>
       </c>
       <c r="R26" t="n">
-        <v>7068304</v>
+        <v>7068449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,12 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,22 +3425,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126290293</v>
+        <v>126290096</v>
       </c>
       <c r="B27" t="n">
-        <v>91534</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,34 +3448,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585692</v>
+        <v>585620</v>
       </c>
       <c r="R27" t="n">
-        <v>7068358</v>
+        <v>7068304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3517,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3527,7 +3522,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,22 +3542,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290817</v>
+        <v>126290293</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>91534</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585783</v>
+        <v>585692</v>
       </c>
       <c r="R28" t="n">
-        <v>7068449</v>
+        <v>7068358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126292842</v>
+        <v>126290524</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585372</v>
+        <v>585691</v>
       </c>
       <c r="R2" t="n">
-        <v>7068719</v>
+        <v>7068379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,66 +780,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126292486</v>
+        <v>126290751</v>
       </c>
       <c r="B3" t="n">
-        <v>100500</v>
+        <v>82789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585542</v>
+        <v>585738</v>
       </c>
       <c r="R3" t="n">
-        <v>7068714</v>
+        <v>7068436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126290751</v>
+        <v>126291209</v>
       </c>
       <c r="B4" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585738</v>
+        <v>585816</v>
       </c>
       <c r="R4" t="n">
-        <v>7068436</v>
+        <v>7068514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126291209</v>
+        <v>126292842</v>
       </c>
       <c r="B5" t="n">
-        <v>82785</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,34 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585816</v>
+        <v>585372</v>
       </c>
       <c r="R5" t="n">
-        <v>7068514</v>
+        <v>7068719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,38 +1113,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126290524</v>
+        <v>126292486</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>100504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1152,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585691</v>
+        <v>585542</v>
       </c>
       <c r="R6" t="n">
-        <v>7068379</v>
+        <v>7068714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,12 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290158</v>
+        <v>126290462</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,39 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585655</v>
+        <v>585690</v>
       </c>
       <c r="R7" t="n">
-        <v>7068334</v>
+        <v>7068354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,50 +1336,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126292436</v>
+        <v>126290723</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585554</v>
+        <v>585727</v>
       </c>
       <c r="R8" t="n">
-        <v>7068705</v>
+        <v>7068424</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,45 +1443,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126291363</v>
+        <v>126290158</v>
       </c>
       <c r="B9" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585786</v>
+        <v>585655</v>
       </c>
       <c r="R9" t="n">
-        <v>7068528</v>
+        <v>7068334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1528,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126290462</v>
+        <v>126291363</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>98370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585690</v>
+        <v>585786</v>
       </c>
       <c r="R10" t="n">
-        <v>7068354</v>
+        <v>7068528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,45 +1667,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290723</v>
+        <v>126292436</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585727</v>
+        <v>585554</v>
       </c>
       <c r="R11" t="n">
-        <v>7068424</v>
+        <v>7068705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,7 +1787,7 @@
         <v>126292542</v>
       </c>
       <c r="B12" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>126290909</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,50 +2008,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126290050</v>
+        <v>126291293</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>100504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585621</v>
+        <v>585803</v>
       </c>
       <c r="R14" t="n">
-        <v>7068305</v>
+        <v>7068537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,12 +2088,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,45 +2120,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126291293</v>
+        <v>126290050</v>
       </c>
       <c r="B15" t="n">
-        <v>100500</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585803</v>
+        <v>585621</v>
       </c>
       <c r="R15" t="n">
-        <v>7068537</v>
+        <v>7068305</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2240,7 @@
         <v>126290184</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>126290936</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289597</v>
+        <v>126289688</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585536</v>
+        <v>585603</v>
       </c>
       <c r="R19" t="n">
-        <v>7068442</v>
+        <v>7068388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289640</v>
+        <v>126289597</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585569</v>
+        <v>585536</v>
       </c>
       <c r="R20" t="n">
-        <v>7068409</v>
+        <v>7068442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289688</v>
+        <v>126289640</v>
       </c>
       <c r="B21" t="n">
-        <v>92528</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585603</v>
+        <v>585569</v>
       </c>
       <c r="R21" t="n">
-        <v>7068388</v>
+        <v>7068409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2894,49 +2894,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126290647</v>
+        <v>126292504</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585702</v>
+        <v>585531</v>
       </c>
       <c r="R22" t="n">
-        <v>7068400</v>
+        <v>7068717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2978,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126289885</v>
+        <v>126290647</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,7 +3031,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3044,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585626</v>
+        <v>585702</v>
       </c>
       <c r="R23" t="n">
-        <v>7068355</v>
+        <v>7068400</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,7 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,45 +3112,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126292504</v>
+        <v>126289885</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585531</v>
+        <v>585626</v>
       </c>
       <c r="R24" t="n">
-        <v>7068717</v>
+        <v>7068355</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,7 +3226,7 @@
         <v>126290275</v>
       </c>
       <c r="B25" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126290817</v>
+        <v>126290293</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>91538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585783</v>
+        <v>585692</v>
       </c>
       <c r="R26" t="n">
-        <v>7068449</v>
+        <v>7068358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126290096</v>
+        <v>126290817</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,39 +3448,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585620</v>
+        <v>585783</v>
       </c>
       <c r="R27" t="n">
-        <v>7068304</v>
+        <v>7068449</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,12 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,22 +3532,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290293</v>
+        <v>126290096</v>
       </c>
       <c r="B28" t="n">
-        <v>91534</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,34 +3555,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585692</v>
+        <v>585620</v>
       </c>
       <c r="R28" t="n">
-        <v>7068358</v>
+        <v>7068304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3634,7 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,61 +3649,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126293117</v>
+        <v>126292399</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>96475</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585398</v>
+        <v>585561</v>
       </c>
       <c r="R29" t="n">
-        <v>7068685</v>
+        <v>7068688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3745,7 +3741,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,57 +3756,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126292399</v>
+        <v>126292086</v>
       </c>
       <c r="B30" t="n">
-        <v>96471</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585561</v>
+        <v>585618</v>
       </c>
       <c r="R30" t="n">
-        <v>7068688</v>
+        <v>7068681</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3852,7 +3853,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3879,38 +3885,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126292086</v>
+        <v>126293117</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>98349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585618</v>
+        <v>585398</v>
       </c>
       <c r="R31" t="n">
-        <v>7068681</v>
+        <v>7068685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,7 +3959,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3964,12 +3969,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,12 +3984,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3999,7 +3999,7 @@
         <v>126290592</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126289969</v>
+        <v>126292586</v>
       </c>
       <c r="B33" t="n">
-        <v>57649</v>
+        <v>91242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,39 +4123,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585627</v>
+        <v>585511</v>
       </c>
       <c r="R33" t="n">
-        <v>7068315</v>
+        <v>7068717</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4187,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4197,7 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,37 +4219,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126292441</v>
+        <v>126289969</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>57653</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4263,10 +4259,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585552</v>
+        <v>585627</v>
       </c>
       <c r="R34" t="n">
-        <v>7068713</v>
+        <v>7068315</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4294,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4308,7 +4304,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4335,45 +4331,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126292586</v>
+        <v>126292441</v>
       </c>
       <c r="B35" t="n">
-        <v>91238</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585511</v>
+        <v>585552</v>
       </c>
       <c r="R35" t="n">
-        <v>7068717</v>
+        <v>7068713</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,7 +4445,7 @@
         <v>126290250</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>126292425</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>126292404</v>
       </c>
       <c r="B38" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>126292374</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>126290861</v>
       </c>
       <c r="B40" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>126290708</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5093,49 +5093,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126290386</v>
+        <v>126291855</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585690</v>
+        <v>585640</v>
       </c>
       <c r="R42" t="n">
-        <v>7068359</v>
+        <v>7068678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5167,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5177,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5207,7 +5203,7 @@
         <v>126290808</v>
       </c>
       <c r="B43" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5311,45 +5307,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126291855</v>
+        <v>126290386</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585640</v>
+        <v>585690</v>
       </c>
       <c r="R44" t="n">
-        <v>7068678</v>
+        <v>7068359</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,45 +5418,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126292907</v>
+        <v>126289622</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585355</v>
+        <v>585561</v>
       </c>
       <c r="R45" t="n">
-        <v>7068706</v>
+        <v>7068428</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5513,57 +5513,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126289622</v>
+        <v>126292907</v>
       </c>
       <c r="B46" t="n">
-        <v>92528</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585561</v>
+        <v>585355</v>
       </c>
       <c r="R46" t="n">
-        <v>7068428</v>
+        <v>7068706</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5620,12 +5620,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5635,7 +5635,7 @@
         <v>126291922</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126290524</v>
+        <v>126292486</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>100504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585691</v>
+        <v>585542</v>
       </c>
       <c r="R2" t="n">
-        <v>7068379</v>
+        <v>7068714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126290751</v>
+        <v>126290524</v>
       </c>
       <c r="B3" t="n">
-        <v>82789</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585738</v>
+        <v>585691</v>
       </c>
       <c r="R3" t="n">
-        <v>7068436</v>
+        <v>7068379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +896,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126291209</v>
+        <v>126290751</v>
       </c>
       <c r="B4" t="n">
         <v>82789</v>
@@ -934,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585816</v>
+        <v>585738</v>
       </c>
       <c r="R4" t="n">
-        <v>7068514</v>
+        <v>7068436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126292842</v>
+        <v>126291209</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585372</v>
+        <v>585816</v>
       </c>
       <c r="R5" t="n">
-        <v>7068719</v>
+        <v>7068514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126292486</v>
+        <v>126292842</v>
       </c>
       <c r="B6" t="n">
-        <v>100504</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585542</v>
+        <v>585372</v>
       </c>
       <c r="R6" t="n">
-        <v>7068714</v>
+        <v>7068719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,44 +1217,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290462</v>
+        <v>126291363</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585690</v>
+        <v>585786</v>
       </c>
       <c r="R7" t="n">
-        <v>7068354</v>
+        <v>7068528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,45 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126290723</v>
+        <v>126292436</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>98370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585727</v>
+        <v>585554</v>
       </c>
       <c r="R8" t="n">
-        <v>7068424</v>
+        <v>7068705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126290158</v>
+        <v>126290462</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,39 +1464,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585655</v>
+        <v>585690</v>
       </c>
       <c r="R9" t="n">
-        <v>7068334</v>
+        <v>7068354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,12 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126291363</v>
+        <v>126290723</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585786</v>
+        <v>585727</v>
       </c>
       <c r="R10" t="n">
-        <v>7068528</v>
+        <v>7068424</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,50 +1655,50 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126292436</v>
+        <v>126290158</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585554</v>
+        <v>585655</v>
       </c>
       <c r="R11" t="n">
-        <v>7068705</v>
+        <v>7068334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,12 +1772,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2008,45 +2008,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126291293</v>
+        <v>126290050</v>
       </c>
       <c r="B14" t="n">
-        <v>100504</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585803</v>
+        <v>585621</v>
       </c>
       <c r="R14" t="n">
-        <v>7068537</v>
+        <v>7068305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,12 +2093,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,50 +2125,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126290050</v>
+        <v>126291293</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>100504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585621</v>
+        <v>585803</v>
       </c>
       <c r="R15" t="n">
-        <v>7068305</v>
+        <v>7068537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2573,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289688</v>
+        <v>126289597</v>
       </c>
       <c r="B19" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585603</v>
+        <v>585536</v>
       </c>
       <c r="R19" t="n">
-        <v>7068388</v>
+        <v>7068442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289597</v>
+        <v>126289640</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585536</v>
+        <v>585569</v>
       </c>
       <c r="R20" t="n">
-        <v>7068442</v>
+        <v>7068409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289640</v>
+        <v>126289688</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585569</v>
+        <v>585603</v>
       </c>
       <c r="R21" t="n">
-        <v>7068409</v>
+        <v>7068388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3661,45 +3661,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292399</v>
+        <v>126292086</v>
       </c>
       <c r="B29" t="n">
-        <v>96475</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585561</v>
+        <v>585618</v>
       </c>
       <c r="R29" t="n">
-        <v>7068688</v>
+        <v>7068681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,7 +3736,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,7 +3746,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,38 +3778,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126292086</v>
+        <v>126293117</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3808,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585618</v>
+        <v>585398</v>
       </c>
       <c r="R30" t="n">
-        <v>7068681</v>
+        <v>7068685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,7 +3852,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,12 +3862,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,19 +3877,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126293117</v>
+        <v>126290592</v>
       </c>
       <c r="B31" t="n">
         <v>98349</v>
@@ -3915,7 +3919,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3924,10 +3933,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585398</v>
+        <v>585701</v>
       </c>
       <c r="R31" t="n">
-        <v>7068685</v>
+        <v>7068380</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3959,7 +3968,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3969,7 +3978,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,66 +3993,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126290592</v>
+        <v>126292399</v>
       </c>
       <c r="B32" t="n">
-        <v>98349</v>
+        <v>96475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585701</v>
+        <v>585561</v>
       </c>
       <c r="R32" t="n">
-        <v>7068380</v>
+        <v>7068688</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126292486</v>
+        <v>126290751</v>
       </c>
       <c r="B2" t="n">
-        <v>100504</v>
+        <v>82789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1365</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585542</v>
+        <v>585738</v>
       </c>
       <c r="R2" t="n">
-        <v>7068714</v>
+        <v>7068436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126290524</v>
+        <v>126291209</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>82789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585691</v>
+        <v>585816</v>
       </c>
       <c r="R3" t="n">
-        <v>7068379</v>
+        <v>7068514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,57 +877,66 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126290751</v>
+        <v>126292486</v>
       </c>
       <c r="B4" t="n">
-        <v>82789</v>
+        <v>100507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585738</v>
+        <v>585542</v>
       </c>
       <c r="R4" t="n">
-        <v>7068436</v>
+        <v>7068714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126291209</v>
+        <v>126292842</v>
       </c>
       <c r="B5" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585816</v>
+        <v>585372</v>
       </c>
       <c r="R5" t="n">
-        <v>7068514</v>
+        <v>7068719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126292842</v>
+        <v>126290524</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,34 +1123,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585372</v>
+        <v>585691</v>
       </c>
       <c r="R6" t="n">
-        <v>7068719</v>
+        <v>7068379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1197,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,44 +1217,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126291363</v>
+        <v>126290462</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585786</v>
+        <v>585690</v>
       </c>
       <c r="R7" t="n">
-        <v>7068528</v>
+        <v>7068354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,50 +1336,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126292436</v>
+        <v>126290723</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585554</v>
+        <v>585727</v>
       </c>
       <c r="R8" t="n">
-        <v>7068705</v>
+        <v>7068424</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,32 +1443,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126290462</v>
+        <v>126291363</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585690</v>
+        <v>585786</v>
       </c>
       <c r="R9" t="n">
-        <v>7068354</v>
+        <v>7068528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,45 +1550,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126290723</v>
+        <v>126292436</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585727</v>
+        <v>585554</v>
       </c>
       <c r="R10" t="n">
-        <v>7068424</v>
+        <v>7068705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1635,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,7 +1787,7 @@
         <v>126292542</v>
       </c>
       <c r="B12" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>126291293</v>
       </c>
       <c r="B15" t="n">
-        <v>100504</v>
+        <v>100507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>126290647</v>
       </c>
       <c r="B23" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>126289885</v>
       </c>
       <c r="B24" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3661,50 +3661,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292086</v>
+        <v>126292399</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>96478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585618</v>
+        <v>585561</v>
       </c>
       <c r="R29" t="n">
-        <v>7068681</v>
+        <v>7068688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3746,12 +3741,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,37 +3768,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126293117</v>
+        <v>126292086</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,10 +3808,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585398</v>
+        <v>585618</v>
       </c>
       <c r="R30" t="n">
-        <v>7068685</v>
+        <v>7068681</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3852,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3862,7 +3853,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3877,22 +3873,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126290592</v>
+        <v>126293117</v>
       </c>
       <c r="B31" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3919,12 +3915,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3933,10 +3924,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585701</v>
+        <v>585398</v>
       </c>
       <c r="R31" t="n">
-        <v>7068380</v>
+        <v>7068685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3968,7 +3959,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3978,7 +3969,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,57 +3984,66 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126292399</v>
+        <v>126290592</v>
       </c>
       <c r="B32" t="n">
-        <v>96475</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585561</v>
+        <v>585701</v>
       </c>
       <c r="R32" t="n">
-        <v>7068688</v>
+        <v>7068380</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4334,7 +4334,7 @@
         <v>126292441</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>126292404</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>126290861</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>126290708</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5200,45 +5200,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126290808</v>
+        <v>126290386</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585766</v>
+        <v>585690</v>
       </c>
       <c r="R43" t="n">
-        <v>7068452</v>
+        <v>7068359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5280,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,49 +5311,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126290386</v>
+        <v>126290808</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>98373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585690</v>
+        <v>585766</v>
       </c>
       <c r="R44" t="n">
-        <v>7068359</v>
+        <v>7068452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126290751</v>
+        <v>126292842</v>
       </c>
       <c r="B2" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585738</v>
+        <v>585372</v>
       </c>
       <c r="R2" t="n">
-        <v>7068436</v>
+        <v>7068719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126291209</v>
+        <v>126290524</v>
       </c>
       <c r="B3" t="n">
-        <v>82789</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585816</v>
+        <v>585691</v>
       </c>
       <c r="R3" t="n">
-        <v>7068514</v>
+        <v>7068379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,66 +887,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126292486</v>
+        <v>126290751</v>
       </c>
       <c r="B4" t="n">
-        <v>100507</v>
+        <v>82789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585542</v>
+        <v>585738</v>
       </c>
       <c r="R4" t="n">
-        <v>7068714</v>
+        <v>7068436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126292842</v>
+        <v>126291209</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,34 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585372</v>
+        <v>585816</v>
       </c>
       <c r="R5" t="n">
-        <v>7068719</v>
+        <v>7068514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,38 +1113,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126290524</v>
+        <v>126292486</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>100507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1152,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585691</v>
+        <v>585542</v>
       </c>
       <c r="R6" t="n">
-        <v>7068379</v>
+        <v>7068714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,12 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290462</v>
+        <v>126291363</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585690</v>
+        <v>585786</v>
       </c>
       <c r="R7" t="n">
-        <v>7068354</v>
+        <v>7068528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,45 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126290723</v>
+        <v>126292436</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585727</v>
+        <v>585554</v>
       </c>
       <c r="R8" t="n">
-        <v>7068424</v>
+        <v>7068705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,32 +1453,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126291363</v>
+        <v>126290462</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585786</v>
+        <v>585690</v>
       </c>
       <c r="R9" t="n">
-        <v>7068528</v>
+        <v>7068354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,50 +1560,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126292436</v>
+        <v>126290723</v>
       </c>
       <c r="B10" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585554</v>
+        <v>585727</v>
       </c>
       <c r="R10" t="n">
-        <v>7068705</v>
+        <v>7068424</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2894,45 +2894,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126292504</v>
+        <v>126290647</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585531</v>
+        <v>585702</v>
       </c>
       <c r="R22" t="n">
-        <v>7068717</v>
+        <v>7068400</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2964,7 +2968,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2974,7 +2978,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126290647</v>
+        <v>126289885</v>
       </c>
       <c r="B23" t="n">
         <v>98352</v>
@@ -3031,7 +3035,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585702</v>
+        <v>585626</v>
       </c>
       <c r="R23" t="n">
-        <v>7068400</v>
+        <v>7068355</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3075,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3089,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,49 +3116,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126289885</v>
+        <v>126292504</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585626</v>
+        <v>585531</v>
       </c>
       <c r="R24" t="n">
-        <v>7068355</v>
+        <v>7068717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3661,45 +3661,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292399</v>
+        <v>126292086</v>
       </c>
       <c r="B29" t="n">
-        <v>96478</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585561</v>
+        <v>585618</v>
       </c>
       <c r="R29" t="n">
-        <v>7068688</v>
+        <v>7068681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,7 +3736,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,7 +3746,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,50 +3778,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126292086</v>
+        <v>126292399</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>96478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585618</v>
+        <v>585561</v>
       </c>
       <c r="R30" t="n">
-        <v>7068681</v>
+        <v>7068688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,7 +3848,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,12 +3858,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4219,38 +4219,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126289969</v>
+        <v>126292441</v>
       </c>
       <c r="B34" t="n">
-        <v>57653</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4259,10 +4258,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585627</v>
+        <v>585552</v>
       </c>
       <c r="R34" t="n">
-        <v>7068315</v>
+        <v>7068713</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,37 +4330,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126292441</v>
+        <v>126289969</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>57653</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585552</v>
+        <v>585627</v>
       </c>
       <c r="R35" t="n">
-        <v>7068713</v>
+        <v>7068315</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4549,32 +4549,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126292425</v>
+        <v>126292404</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
         <v>585557</v>
       </c>
       <c r="R37" t="n">
-        <v>7068702</v>
+        <v>7068699</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4656,32 +4656,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126292404</v>
+        <v>126292425</v>
       </c>
       <c r="B38" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
         <v>585557</v>
       </c>
       <c r="R38" t="n">
-        <v>7068699</v>
+        <v>7068702</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5093,45 +5093,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126291855</v>
+        <v>126290386</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585640</v>
+        <v>585690</v>
       </c>
       <c r="R42" t="n">
-        <v>7068678</v>
+        <v>7068359</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5177,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,49 +5204,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126290386</v>
+        <v>126291855</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585690</v>
+        <v>585640</v>
       </c>
       <c r="R43" t="n">
-        <v>7068359</v>
+        <v>7068678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126292842</v>
+        <v>126290751</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585372</v>
+        <v>585738</v>
       </c>
       <c r="R2" t="n">
-        <v>7068719</v>
+        <v>7068436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126290524</v>
+        <v>126291209</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>82789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585691</v>
+        <v>585816</v>
       </c>
       <c r="R3" t="n">
-        <v>7068379</v>
+        <v>7068514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,57 +877,66 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126290751</v>
+        <v>126292486</v>
       </c>
       <c r="B4" t="n">
-        <v>82789</v>
+        <v>100507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585738</v>
+        <v>585542</v>
       </c>
       <c r="R4" t="n">
-        <v>7068436</v>
+        <v>7068714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126291209</v>
+        <v>126290524</v>
       </c>
       <c r="B5" t="n">
-        <v>82789</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1016,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585816</v>
+        <v>585691</v>
       </c>
       <c r="R5" t="n">
-        <v>7068514</v>
+        <v>7068379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,66 +1110,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126292486</v>
+        <v>126292842</v>
       </c>
       <c r="B6" t="n">
-        <v>100507</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585542</v>
+        <v>585372</v>
       </c>
       <c r="R6" t="n">
-        <v>7068714</v>
+        <v>7068719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,57 +1217,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126291363</v>
+        <v>126290158</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585786</v>
+        <v>585655</v>
       </c>
       <c r="R7" t="n">
-        <v>7068528</v>
+        <v>7068334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,50 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126292436</v>
+        <v>126290462</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>91242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585554</v>
+        <v>585690</v>
       </c>
       <c r="R8" t="n">
-        <v>7068705</v>
+        <v>7068354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126290462</v>
+        <v>126290723</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,21 +1464,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585690</v>
+        <v>585727</v>
       </c>
       <c r="R9" t="n">
-        <v>7068354</v>
+        <v>7068424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,44 +1548,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126290723</v>
+        <v>126291363</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585727</v>
+        <v>585786</v>
       </c>
       <c r="R10" t="n">
-        <v>7068424</v>
+        <v>7068528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,50 +1655,50 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290158</v>
+        <v>126292436</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585655</v>
+        <v>585554</v>
       </c>
       <c r="R11" t="n">
-        <v>7068334</v>
+        <v>7068705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,57 +1772,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126292542</v>
+        <v>126290909</v>
       </c>
       <c r="B12" t="n">
-        <v>96478</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585526</v>
+        <v>585834</v>
       </c>
       <c r="R12" t="n">
-        <v>7068711</v>
+        <v>7068491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1869,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,62 +1889,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126290909</v>
+        <v>126292542</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>96478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585834</v>
+        <v>585526</v>
       </c>
       <c r="R13" t="n">
-        <v>7068491</v>
+        <v>7068711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1971,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,12 +1981,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,12 +1996,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2573,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289597</v>
+        <v>126289688</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585536</v>
+        <v>585603</v>
       </c>
       <c r="R19" t="n">
-        <v>7068442</v>
+        <v>7068388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289640</v>
+        <v>126289597</v>
       </c>
       <c r="B20" t="n">
         <v>78977</v>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585569</v>
+        <v>585536</v>
       </c>
       <c r="R20" t="n">
-        <v>7068409</v>
+        <v>7068442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289688</v>
+        <v>126289640</v>
       </c>
       <c r="B21" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585603</v>
+        <v>585569</v>
       </c>
       <c r="R21" t="n">
-        <v>7068388</v>
+        <v>7068409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2894,49 +2894,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126290647</v>
+        <v>126292504</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585702</v>
+        <v>585531</v>
       </c>
       <c r="R22" t="n">
-        <v>7068400</v>
+        <v>7068717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2978,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,45 +3112,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126292504</v>
+        <v>126290647</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585531</v>
+        <v>585702</v>
       </c>
       <c r="R24" t="n">
-        <v>7068717</v>
+        <v>7068400</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126290293</v>
+        <v>126290817</v>
       </c>
       <c r="B26" t="n">
-        <v>91538</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585692</v>
+        <v>585783</v>
       </c>
       <c r="R26" t="n">
-        <v>7068358</v>
+        <v>7068449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126290817</v>
+        <v>126290096</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,34 +3448,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585783</v>
+        <v>585620</v>
       </c>
       <c r="R27" t="n">
-        <v>7068449</v>
+        <v>7068304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3522,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3532,22 +3542,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290096</v>
+        <v>126290293</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>91538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,39 +3565,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585620</v>
+        <v>585692</v>
       </c>
       <c r="R28" t="n">
-        <v>7068304</v>
+        <v>7068358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3634,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,50 +3649,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292086</v>
+        <v>126293117</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3701,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585618</v>
+        <v>585398</v>
       </c>
       <c r="R29" t="n">
-        <v>7068681</v>
+        <v>7068685</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,7 +3735,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3746,12 +3745,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3766,57 +3760,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126292399</v>
+        <v>126290592</v>
       </c>
       <c r="B30" t="n">
-        <v>96478</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585561</v>
+        <v>585701</v>
       </c>
       <c r="R30" t="n">
-        <v>7068688</v>
+        <v>7068380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3848,7 +3851,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,49 +3888,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126293117</v>
+        <v>126292399</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>96478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585398</v>
+        <v>585561</v>
       </c>
       <c r="R31" t="n">
-        <v>7068685</v>
+        <v>7068688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3959,7 +3958,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3969,7 +3968,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,54 +3983,50 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126290592</v>
+        <v>126292086</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585701</v>
+        <v>585618</v>
       </c>
       <c r="R32" t="n">
-        <v>7068380</v>
+        <v>7068681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4070,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4085,7 +4080,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,45 +4112,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126292586</v>
+        <v>126292441</v>
       </c>
       <c r="B33" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585511</v>
+        <v>585552</v>
       </c>
       <c r="R33" t="n">
-        <v>7068717</v>
+        <v>7068713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4186,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4196,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,49 +4223,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126292441</v>
+        <v>126292586</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585552</v>
+        <v>585511</v>
       </c>
       <c r="R34" t="n">
-        <v>7068713</v>
+        <v>7068717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4549,32 +4549,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126292404</v>
+        <v>126292425</v>
       </c>
       <c r="B37" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
         <v>585557</v>
       </c>
       <c r="R37" t="n">
-        <v>7068699</v>
+        <v>7068702</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4656,32 +4656,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126292425</v>
+        <v>126292404</v>
       </c>
       <c r="B38" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
         <v>585557</v>
       </c>
       <c r="R38" t="n">
-        <v>7068702</v>
+        <v>7068699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4870,45 +4870,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126290861</v>
+        <v>126290708</v>
       </c>
       <c r="B40" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585819</v>
+        <v>585732</v>
       </c>
       <c r="R40" t="n">
-        <v>7068495</v>
+        <v>7068429</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4949,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4959,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,66 +4974,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126290708</v>
+        <v>126290861</v>
       </c>
       <c r="B41" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585732</v>
+        <v>585819</v>
       </c>
       <c r="R41" t="n">
-        <v>7068429</v>
+        <v>7068495</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,61 +5081,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126290386</v>
+        <v>126291855</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585690</v>
+        <v>585640</v>
       </c>
       <c r="R42" t="n">
-        <v>7068359</v>
+        <v>7068678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5167,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5177,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5204,45 +5200,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126291855</v>
+        <v>126290386</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585640</v>
+        <v>585690</v>
       </c>
       <c r="R43" t="n">
-        <v>7068678</v>
+        <v>7068359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -1784,50 +1784,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126290909</v>
+        <v>126292542</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>96478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585834</v>
+        <v>585526</v>
       </c>
       <c r="R12" t="n">
-        <v>7068491</v>
+        <v>7068711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,12 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,57 +1879,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126292542</v>
+        <v>126290909</v>
       </c>
       <c r="B13" t="n">
-        <v>96478</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585526</v>
+        <v>585834</v>
       </c>
       <c r="R13" t="n">
-        <v>7068711</v>
+        <v>7068491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1981,7 +1976,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,62 +1996,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126290050</v>
+        <v>126291293</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>100507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585621</v>
+        <v>585803</v>
       </c>
       <c r="R14" t="n">
-        <v>7068305</v>
+        <v>7068537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,12 +2088,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,45 +2120,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126291293</v>
+        <v>126290050</v>
       </c>
       <c r="B15" t="n">
-        <v>100507</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585803</v>
+        <v>585621</v>
       </c>
       <c r="R15" t="n">
-        <v>7068537</v>
+        <v>7068305</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3661,49 +3661,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126293117</v>
+        <v>126292399</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>96478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585398</v>
+        <v>585561</v>
       </c>
       <c r="R29" t="n">
-        <v>7068685</v>
+        <v>7068688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3745,7 +3741,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,54 +3756,50 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126290592</v>
+        <v>126292086</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3816,10 +3808,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585701</v>
+        <v>585618</v>
       </c>
       <c r="R30" t="n">
-        <v>7068380</v>
+        <v>7068681</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3851,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3861,7 +3853,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3888,45 +3885,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126292399</v>
+        <v>126293117</v>
       </c>
       <c r="B31" t="n">
-        <v>96478</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585561</v>
+        <v>585398</v>
       </c>
       <c r="R31" t="n">
-        <v>7068688</v>
+        <v>7068685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3958,7 +3959,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3968,7 +3969,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,50 +3984,54 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126292086</v>
+        <v>126290592</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585618</v>
+        <v>585701</v>
       </c>
       <c r="R32" t="n">
-        <v>7068681</v>
+        <v>7068380</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,7 +4075,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4080,12 +4085,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126290751</v>
       </c>
       <c r="B2" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126291209</v>
       </c>
       <c r="B3" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126292486</v>
       </c>
       <c r="B4" t="n">
-        <v>100507</v>
+        <v>100516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126290524</v>
+        <v>126292842</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585691</v>
+        <v>585372</v>
       </c>
       <c r="R5" t="n">
-        <v>7068379</v>
+        <v>7068719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1100,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126292842</v>
+        <v>126290524</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,34 +1123,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585372</v>
+        <v>585691</v>
       </c>
       <c r="R6" t="n">
-        <v>7068719</v>
+        <v>7068379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1197,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,12 +1217,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
         <v>126290158</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>126290462</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>126290723</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>126291363</v>
       </c>
       <c r="B10" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>126292436</v>
       </c>
       <c r="B11" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>126292542</v>
       </c>
       <c r="B12" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>126290909</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>126291293</v>
       </c>
       <c r="B14" t="n">
-        <v>100507</v>
+        <v>100516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>126290050</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126290184</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>126290936</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289688</v>
+        <v>126289597</v>
       </c>
       <c r="B19" t="n">
-        <v>92532</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585603</v>
+        <v>585536</v>
       </c>
       <c r="R19" t="n">
-        <v>7068388</v>
+        <v>7068442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289597</v>
+        <v>126289640</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585536</v>
+        <v>585569</v>
       </c>
       <c r="R20" t="n">
-        <v>7068442</v>
+        <v>7068409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289640</v>
+        <v>126289688</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>92535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585569</v>
+        <v>585603</v>
       </c>
       <c r="R21" t="n">
-        <v>7068409</v>
+        <v>7068388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,7 +2897,7 @@
         <v>126292504</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126289885</v>
+        <v>126290647</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585626</v>
+        <v>585702</v>
       </c>
       <c r="R23" t="n">
-        <v>7068355</v>
+        <v>7068400</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,10 +3112,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126290647</v>
+        <v>126289885</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585702</v>
+        <v>585626</v>
       </c>
       <c r="R24" t="n">
-        <v>7068400</v>
+        <v>7068355</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,7 +3226,7 @@
         <v>126290275</v>
       </c>
       <c r="B25" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126290817</v>
+        <v>126290293</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>91541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585783</v>
+        <v>585692</v>
       </c>
       <c r="R26" t="n">
-        <v>7068449</v>
+        <v>7068358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,7 +3440,7 @@
         <v>126290096</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290293</v>
+        <v>126290817</v>
       </c>
       <c r="B28" t="n">
-        <v>91538</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585692</v>
+        <v>585783</v>
       </c>
       <c r="R28" t="n">
-        <v>7068358</v>
+        <v>7068449</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3661,45 +3661,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292399</v>
+        <v>126292086</v>
       </c>
       <c r="B29" t="n">
-        <v>96478</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585561</v>
+        <v>585618</v>
       </c>
       <c r="R29" t="n">
-        <v>7068688</v>
+        <v>7068681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,7 +3736,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,7 +3746,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,50 +3778,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126292086</v>
+        <v>126292399</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>96487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585618</v>
+        <v>585561</v>
       </c>
       <c r="R30" t="n">
-        <v>7068681</v>
+        <v>7068688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,7 +3848,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,12 +3858,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3888,7 +3888,7 @@
         <v>126293117</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>126290592</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>126292441</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>126292586</v>
       </c>
       <c r="B34" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>126289969</v>
       </c>
       <c r="B35" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>126290250</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>126292425</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>126292404</v>
       </c>
       <c r="B38" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>126292374</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>126290708</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>126290861</v>
       </c>
       <c r="B41" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>126291855</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>126290386</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126290808</v>
       </c>
       <c r="B44" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>126289622</v>
       </c>
       <c r="B45" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>126292907</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>126291922</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290158</v>
+        <v>126290462</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,39 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585655</v>
+        <v>585690</v>
       </c>
       <c r="R7" t="n">
-        <v>7068334</v>
+        <v>7068354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126290462</v>
+        <v>126290723</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585690</v>
+        <v>585727</v>
       </c>
       <c r="R8" t="n">
-        <v>7068354</v>
+        <v>7068424</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,44 +1431,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126290723</v>
+        <v>126291363</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585727</v>
+        <v>585786</v>
       </c>
       <c r="R9" t="n">
-        <v>7068424</v>
+        <v>7068528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,19 +1538,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126291363</v>
+        <v>126292436</v>
       </c>
       <c r="B10" t="n">
         <v>98382</v>
@@ -1589,16 +1579,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585786</v>
+        <v>585554</v>
       </c>
       <c r="R10" t="n">
-        <v>7068528</v>
+        <v>7068705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1635,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,50 +1655,50 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126292436</v>
+        <v>126290158</v>
       </c>
       <c r="B11" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585554</v>
+        <v>585655</v>
       </c>
       <c r="R11" t="n">
-        <v>7068705</v>
+        <v>7068334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,12 +1772,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126290096</v>
+        <v>126290817</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,39 +3448,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585620</v>
+        <v>585783</v>
       </c>
       <c r="R27" t="n">
-        <v>7068304</v>
+        <v>7068449</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,12 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,22 +3532,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290817</v>
+        <v>126290096</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,34 +3555,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585783</v>
+        <v>585620</v>
       </c>
       <c r="R28" t="n">
-        <v>7068449</v>
+        <v>7068304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3634,7 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,62 +3649,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292086</v>
+        <v>126292399</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>96487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585618</v>
+        <v>585561</v>
       </c>
       <c r="R29" t="n">
-        <v>7068681</v>
+        <v>7068688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3746,12 +3741,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,45 +3768,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126292399</v>
+        <v>126293117</v>
       </c>
       <c r="B30" t="n">
-        <v>96487</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585561</v>
+        <v>585398</v>
       </c>
       <c r="R30" t="n">
-        <v>7068688</v>
+        <v>7068685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3848,7 +3842,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3858,7 +3852,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,19 +3867,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126293117</v>
+        <v>126290592</v>
       </c>
       <c r="B31" t="n">
         <v>98361</v>
@@ -3915,7 +3909,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3924,10 +3923,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585398</v>
+        <v>585701</v>
       </c>
       <c r="R31" t="n">
-        <v>7068685</v>
+        <v>7068380</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3959,7 +3958,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3969,7 +3968,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,54 +3983,50 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126290592</v>
+        <v>126292086</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585701</v>
+        <v>585618</v>
       </c>
       <c r="R32" t="n">
-        <v>7068380</v>
+        <v>7068681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4070,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4085,7 +4080,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290462</v>
+        <v>126290723</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585690</v>
+        <v>585727</v>
       </c>
       <c r="R7" t="n">
-        <v>7068354</v>
+        <v>7068424</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1324,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126290723</v>
+        <v>126290158</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,34 +1347,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585727</v>
+        <v>585655</v>
       </c>
       <c r="R8" t="n">
-        <v>7068424</v>
+        <v>7068334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1667,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290158</v>
+        <v>126290462</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,39 +1688,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585655</v>
+        <v>585690</v>
       </c>
       <c r="R11" t="n">
-        <v>7068334</v>
+        <v>7068354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,12 +1757,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3001,7 +3001,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126290647</v>
+        <v>126289885</v>
       </c>
       <c r="B23" t="n">
         <v>98361</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585702</v>
+        <v>585626</v>
       </c>
       <c r="R23" t="n">
-        <v>7068400</v>
+        <v>7068355</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,7 +3112,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126289885</v>
+        <v>126290647</v>
       </c>
       <c r="B24" t="n">
         <v>98361</v>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585626</v>
+        <v>585702</v>
       </c>
       <c r="R24" t="n">
-        <v>7068355</v>
+        <v>7068400</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126290293</v>
+        <v>126290817</v>
       </c>
       <c r="B26" t="n">
-        <v>91541</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585692</v>
+        <v>585783</v>
       </c>
       <c r="R26" t="n">
-        <v>7068358</v>
+        <v>7068449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126290817</v>
+        <v>126290096</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,34 +3448,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585783</v>
+        <v>585620</v>
       </c>
       <c r="R27" t="n">
-        <v>7068449</v>
+        <v>7068304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3522,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3532,22 +3542,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290096</v>
+        <v>126290293</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>91541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,39 +3565,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585620</v>
+        <v>585692</v>
       </c>
       <c r="R28" t="n">
-        <v>7068304</v>
+        <v>7068358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3634,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,57 +3649,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126292399</v>
+        <v>126293117</v>
       </c>
       <c r="B29" t="n">
-        <v>96487</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585561</v>
+        <v>585398</v>
       </c>
       <c r="R29" t="n">
-        <v>7068688</v>
+        <v>7068685</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,7 +3745,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,19 +3760,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126293117</v>
+        <v>126290592</v>
       </c>
       <c r="B30" t="n">
         <v>98361</v>
@@ -3798,7 +3802,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3807,10 +3816,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585398</v>
+        <v>585701</v>
       </c>
       <c r="R30" t="n">
-        <v>7068685</v>
+        <v>7068380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,7 +3851,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3852,7 +3861,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3867,54 +3876,50 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126290592</v>
+        <v>126292086</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585701</v>
+        <v>585618</v>
       </c>
       <c r="R31" t="n">
-        <v>7068380</v>
+        <v>7068681</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3958,7 +3963,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3968,7 +3973,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3995,50 +4005,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126292086</v>
+        <v>126292399</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>96487</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585618</v>
+        <v>585561</v>
       </c>
       <c r="R32" t="n">
-        <v>7068681</v>
+        <v>7068688</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,7 +4075,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4080,12 +4085,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,49 +4112,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126292441</v>
+        <v>126292586</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585552</v>
+        <v>585511</v>
       </c>
       <c r="R33" t="n">
-        <v>7068713</v>
+        <v>7068717</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4186,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4196,7 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,10 +4219,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126292586</v>
+        <v>126289969</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>57654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,34 +4230,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585511</v>
+        <v>585627</v>
       </c>
       <c r="R34" t="n">
-        <v>7068717</v>
+        <v>7068315</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4294,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4304,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,38 +4331,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126289969</v>
+        <v>126292441</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585627</v>
+        <v>585552</v>
       </c>
       <c r="R35" t="n">
-        <v>7068315</v>
+        <v>7068713</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126291855</v>
+        <v>126290808</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585640</v>
+        <v>585766</v>
       </c>
       <c r="R42" t="n">
-        <v>7068678</v>
+        <v>7068452</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,49 +5200,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126290386</v>
+        <v>126291855</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585690</v>
+        <v>585640</v>
       </c>
       <c r="R43" t="n">
-        <v>7068359</v>
+        <v>7068678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,7 +5270,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5280,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,45 +5307,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126290808</v>
+        <v>126290386</v>
       </c>
       <c r="B44" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585766</v>
+        <v>585690</v>
       </c>
       <c r="R44" t="n">
-        <v>7068452</v>
+        <v>7068359</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,32 +5418,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126289622</v>
+        <v>126291922</v>
       </c>
       <c r="B45" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585561</v>
+        <v>585613</v>
       </c>
       <c r="R45" t="n">
-        <v>7068428</v>
+        <v>7068689</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5513,12 +5513,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5632,32 +5632,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126291922</v>
+        <v>126289622</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585613</v>
+        <v>585561</v>
       </c>
       <c r="R47" t="n">
-        <v>7068689</v>
+        <v>7068428</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5727,12 +5727,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290723</v>
+        <v>126291363</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>98382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585727</v>
+        <v>585786</v>
       </c>
       <c r="R7" t="n">
-        <v>7068424</v>
+        <v>7068528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,50 +1324,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126290158</v>
+        <v>126292436</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585655</v>
+        <v>585554</v>
       </c>
       <c r="R8" t="n">
-        <v>7068334</v>
+        <v>7068705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,44 +1441,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126291363</v>
+        <v>126290723</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585786</v>
+        <v>585727</v>
       </c>
       <c r="R9" t="n">
-        <v>7068528</v>
+        <v>7068424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,62 +1548,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126292436</v>
+        <v>126290462</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585554</v>
+        <v>585690</v>
       </c>
       <c r="R10" t="n">
-        <v>7068705</v>
+        <v>7068354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,22 +1655,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290462</v>
+        <v>126290158</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,34 +1678,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585690</v>
+        <v>585655</v>
       </c>
       <c r="R11" t="n">
-        <v>7068354</v>
+        <v>7068334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2573,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289597</v>
+        <v>126289688</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585536</v>
+        <v>585603</v>
       </c>
       <c r="R19" t="n">
-        <v>7068442</v>
+        <v>7068388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289640</v>
+        <v>126289597</v>
       </c>
       <c r="B20" t="n">
         <v>78980</v>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585569</v>
+        <v>585536</v>
       </c>
       <c r="R20" t="n">
-        <v>7068409</v>
+        <v>7068442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289688</v>
+        <v>126289640</v>
       </c>
       <c r="B21" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585603</v>
+        <v>585569</v>
       </c>
       <c r="R21" t="n">
-        <v>7068388</v>
+        <v>7068409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4112,45 +4112,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126292586</v>
+        <v>126292441</v>
       </c>
       <c r="B33" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585511</v>
+        <v>585552</v>
       </c>
       <c r="R33" t="n">
-        <v>7068717</v>
+        <v>7068713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4186,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4196,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,10 +4223,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126289969</v>
+        <v>126292586</v>
       </c>
       <c r="B34" t="n">
-        <v>57654</v>
+        <v>91245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4230,39 +4234,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585627</v>
+        <v>585511</v>
       </c>
       <c r="R34" t="n">
-        <v>7068315</v>
+        <v>7068717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,37 +4330,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126292441</v>
+        <v>126289969</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585552</v>
+        <v>585627</v>
       </c>
       <c r="R35" t="n">
-        <v>7068713</v>
+        <v>7068315</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126290808</v>
+        <v>126291855</v>
       </c>
       <c r="B42" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585766</v>
+        <v>585640</v>
       </c>
       <c r="R42" t="n">
-        <v>7068452</v>
+        <v>7068678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,45 +5200,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126291855</v>
+        <v>126290386</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585640</v>
+        <v>585690</v>
       </c>
       <c r="R43" t="n">
-        <v>7068678</v>
+        <v>7068359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5280,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,49 +5311,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126290386</v>
+        <v>126290808</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585690</v>
+        <v>585766</v>
       </c>
       <c r="R44" t="n">
-        <v>7068359</v>
+        <v>7068452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,32 +5418,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126291922</v>
+        <v>126289622</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585613</v>
+        <v>585561</v>
       </c>
       <c r="R45" t="n">
-        <v>7068689</v>
+        <v>7068428</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5513,19 +5513,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126292907</v>
+        <v>126291922</v>
       </c>
       <c r="B46" t="n">
         <v>78980</v>
@@ -5556,14 +5556,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585355</v>
+        <v>585613</v>
       </c>
       <c r="R46" t="n">
-        <v>7068706</v>
+        <v>7068689</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5632,45 +5632,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126289622</v>
+        <v>126292907</v>
       </c>
       <c r="B47" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585561</v>
+        <v>585355</v>
       </c>
       <c r="R47" t="n">
-        <v>7068428</v>
+        <v>7068706</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5727,12 +5727,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126291855</v>
+        <v>126290808</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585640</v>
+        <v>585766</v>
       </c>
       <c r="R42" t="n">
-        <v>7068678</v>
+        <v>7068452</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,49 +5200,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126290386</v>
+        <v>126291855</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585690</v>
+        <v>585640</v>
       </c>
       <c r="R43" t="n">
-        <v>7068359</v>
+        <v>7068678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,7 +5270,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5280,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,45 +5307,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126290808</v>
+        <v>126290386</v>
       </c>
       <c r="B44" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585766</v>
+        <v>585690</v>
       </c>
       <c r="R44" t="n">
-        <v>7068452</v>
+        <v>7068359</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -2573,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289688</v>
+        <v>126289597</v>
       </c>
       <c r="B19" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585603</v>
+        <v>585536</v>
       </c>
       <c r="R19" t="n">
-        <v>7068388</v>
+        <v>7068442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289597</v>
+        <v>126289640</v>
       </c>
       <c r="B20" t="n">
         <v>78980</v>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585536</v>
+        <v>585569</v>
       </c>
       <c r="R20" t="n">
-        <v>7068442</v>
+        <v>7068409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289640</v>
+        <v>126289688</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585569</v>
+        <v>585603</v>
       </c>
       <c r="R21" t="n">
-        <v>7068409</v>
+        <v>7068388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -5093,32 +5093,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126290808</v>
+        <v>126291855</v>
       </c>
       <c r="B42" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585766</v>
+        <v>585640</v>
       </c>
       <c r="R42" t="n">
-        <v>7068452</v>
+        <v>7068678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,45 +5200,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126291855</v>
+        <v>126290386</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585640</v>
+        <v>585690</v>
       </c>
       <c r="R43" t="n">
-        <v>7068678</v>
+        <v>7068359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5280,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,49 +5311,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126290386</v>
+        <v>126290808</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585690</v>
+        <v>585766</v>
       </c>
       <c r="R44" t="n">
-        <v>7068359</v>
+        <v>7068452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126290751</v>
+        <v>126290293</v>
       </c>
       <c r="B2" t="n">
-        <v>82792</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585738</v>
+        <v>585692</v>
       </c>
       <c r="R2" t="n">
-        <v>7068436</v>
+        <v>7068358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126291209</v>
+        <v>126290275</v>
       </c>
       <c r="B3" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585816</v>
+        <v>585688</v>
       </c>
       <c r="R3" t="n">
-        <v>7068514</v>
+        <v>7068356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126292486</v>
+        <v>126290462</v>
       </c>
       <c r="B4" t="n">
-        <v>100516</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585542</v>
+        <v>585690</v>
       </c>
       <c r="R4" t="n">
-        <v>7068714</v>
+        <v>7068354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126292842</v>
+        <v>126292586</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585372</v>
+        <v>585511</v>
       </c>
       <c r="R5" t="n">
-        <v>7068719</v>
+        <v>7068717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126290524</v>
+        <v>126290751</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585691</v>
+        <v>585738</v>
       </c>
       <c r="R6" t="n">
-        <v>7068379</v>
+        <v>7068436</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126290723</v>
+        <v>126291209</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585727</v>
+        <v>585816</v>
       </c>
       <c r="R7" t="n">
-        <v>7068424</v>
+        <v>7068514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,62 +1305,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126290158</v>
+        <v>126291293</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>101299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585655</v>
+        <v>585803</v>
       </c>
       <c r="R8" t="n">
-        <v>7068334</v>
+        <v>7068537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1397,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126291363</v>
+        <v>126292486</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>101299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,34 +1440,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585786</v>
+        <v>585542</v>
       </c>
       <c r="R9" t="n">
-        <v>7068528</v>
+        <v>7068714</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1533,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126292436</v>
+        <v>126292399</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>97231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,39 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585554</v>
+        <v>585561</v>
       </c>
       <c r="R10" t="n">
-        <v>7068705</v>
+        <v>7068688</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,12 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,32 +1652,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290462</v>
+        <v>126292542</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585690</v>
+        <v>585526</v>
       </c>
       <c r="R11" t="n">
-        <v>7068354</v>
+        <v>7068711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126292542</v>
+        <v>126289622</v>
       </c>
       <c r="B12" t="n">
-        <v>96487</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1819,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585526</v>
+        <v>585561</v>
       </c>
       <c r="R12" t="n">
-        <v>7068711</v>
+        <v>7068428</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,22 +1854,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126290909</v>
+        <v>126289688</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,39 +1877,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585834</v>
+        <v>585603</v>
       </c>
       <c r="R13" t="n">
-        <v>7068491</v>
+        <v>7068388</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,12 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,44 +1961,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126291293</v>
+        <v>126289597</v>
       </c>
       <c r="B14" t="n">
-        <v>100516</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585803</v>
+        <v>585536</v>
       </c>
       <c r="R14" t="n">
-        <v>7068537</v>
+        <v>7068442</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,12 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,50 +2080,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126290050</v>
+        <v>126289640</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585621</v>
+        <v>585569</v>
       </c>
       <c r="R15" t="n">
-        <v>7068305</v>
+        <v>7068409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2205,12 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,11 +2190,11 @@
         <v>126290184</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2344,50 +2294,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126290181</v>
+        <v>126290250</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585655</v>
+        <v>585669</v>
       </c>
       <c r="R17" t="n">
-        <v>7068320</v>
+        <v>7068341</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2429,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,62 +2389,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126290936</v>
+        <v>126290817</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585823</v>
+        <v>585783</v>
       </c>
       <c r="R18" t="n">
-        <v>7068501</v>
+        <v>7068449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2541,12 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126289688</v>
+        <v>126291855</v>
       </c>
       <c r="B19" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585603</v>
+        <v>585640</v>
       </c>
       <c r="R19" t="n">
-        <v>7068388</v>
+        <v>7068678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,14 +2615,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126289597</v>
+        <v>126291922</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2715,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585536</v>
+        <v>585613</v>
       </c>
       <c r="R20" t="n">
-        <v>7068442</v>
+        <v>7068689</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,14 +2722,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126289640</v>
+        <v>126292374</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2822,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585569</v>
+        <v>585578</v>
       </c>
       <c r="R21" t="n">
-        <v>7068409</v>
+        <v>7068675</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2792,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2802,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2894,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126289885</v>
+        <v>126292504</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,38 +2840,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585626</v>
+        <v>585531</v>
       </c>
       <c r="R22" t="n">
-        <v>7068355</v>
+        <v>7068717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,7 +2899,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2978,7 +2909,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126290647</v>
+        <v>126292842</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,38 +2947,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585702</v>
+        <v>585372</v>
       </c>
       <c r="R23" t="n">
-        <v>7068400</v>
+        <v>7068719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,7 +3006,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,7 +3016,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,14 +3043,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126292504</v>
+        <v>126292907</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3147,14 +3074,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585531</v>
+        <v>585355</v>
       </c>
       <c r="R24" t="n">
-        <v>7068717</v>
+        <v>7068706</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126290275</v>
+        <v>126290723</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,21 +3161,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3258,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585688</v>
+        <v>585727</v>
       </c>
       <c r="R25" t="n">
-        <v>7068356</v>
+        <v>7068424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,7 +3220,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3230,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,22 +3245,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126290817</v>
+        <v>126292425</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3268,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3292,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585783</v>
+        <v>585557</v>
       </c>
       <c r="R26" t="n">
-        <v>7068449</v>
+        <v>7068702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,7 +3327,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3337,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,27 +3364,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126290096</v>
+        <v>126289969</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3477,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585620</v>
+        <v>585627</v>
       </c>
       <c r="R27" t="n">
-        <v>7068304</v>
+        <v>7068315</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3512,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,12 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,22 +3464,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126290293</v>
+        <v>126290050</v>
       </c>
       <c r="B28" t="n">
-        <v>91541</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,34 +3487,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585692</v>
+        <v>585621</v>
       </c>
       <c r="R28" t="n">
-        <v>7068358</v>
+        <v>7068305</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,7 +3551,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3634,7 +3561,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3661,37 +3593,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126293117</v>
+        <v>126290096</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3700,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585398</v>
+        <v>585620</v>
       </c>
       <c r="R29" t="n">
-        <v>7068685</v>
+        <v>7068304</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3745,7 +3678,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,54 +3698,50 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126290592</v>
+        <v>126290158</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3816,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585701</v>
+        <v>585655</v>
       </c>
       <c r="R30" t="n">
-        <v>7068380</v>
+        <v>7068334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3851,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3861,7 +3795,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3876,22 +3815,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126292086</v>
+        <v>126290209</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3919,7 +3858,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,10 +3867,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585618</v>
+        <v>585665</v>
       </c>
       <c r="R31" t="n">
-        <v>7068681</v>
+        <v>7068312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3963,7 +3902,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3973,12 +3912,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall, färska och äldre spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,57 +3932,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126292399</v>
+        <v>126290524</v>
       </c>
       <c r="B32" t="n">
-        <v>96487</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585561</v>
+        <v>585691</v>
       </c>
       <c r="R32" t="n">
-        <v>7068688</v>
+        <v>7068379</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4085,7 +4029,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,37 +4061,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126292441</v>
+        <v>126290909</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4151,10 +4101,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585552</v>
+        <v>585834</v>
       </c>
       <c r="R33" t="n">
-        <v>7068713</v>
+        <v>7068491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4186,7 +4136,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4196,7 +4146,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4211,22 +4166,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126292586</v>
+        <v>126290936</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,34 +4189,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585511</v>
+        <v>585823</v>
       </c>
       <c r="R34" t="n">
-        <v>7068717</v>
+        <v>7068501</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4253,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4263,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,10 +4295,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126289969</v>
+        <v>126292086</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,16 +4306,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4370,10 +4335,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585627</v>
+        <v>585618</v>
       </c>
       <c r="R35" t="n">
-        <v>7068315</v>
+        <v>7068681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4370,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4380,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4430,22 +4400,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126290250</v>
+        <v>126292757</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,34 +4423,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Illflobäcken, Illflobäcken, Ång</t>
+          <t>Oxmyran, Oxmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585669</v>
+        <v>585436</v>
       </c>
       <c r="R36" t="n">
-        <v>7068341</v>
+        <v>7068768</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4512,7 +4487,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4522,7 +4497,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,45 +4529,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126292425</v>
+        <v>126290181</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>5179</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585557</v>
+        <v>585655</v>
       </c>
       <c r="R37" t="n">
-        <v>7068702</v>
+        <v>7068320</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4619,7 +4604,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4614,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4644,57 +4629,61 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126292404</v>
+        <v>126289885</v>
       </c>
       <c r="B38" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585557</v>
+        <v>585626</v>
       </c>
       <c r="R38" t="n">
-        <v>7068699</v>
+        <v>7068355</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,7 +4715,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4725,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4763,45 +4752,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126292374</v>
+        <v>126290386</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585578</v>
+        <v>585690</v>
       </c>
       <c r="R39" t="n">
-        <v>7068675</v>
+        <v>7068359</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4826,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4836,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,10 +4863,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126290708</v>
+        <v>126290592</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4900,7 +4893,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4914,10 +4907,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585732</v>
+        <v>585701</v>
       </c>
       <c r="R40" t="n">
-        <v>7068429</v>
+        <v>7068380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4949,7 +4942,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,7 +4952,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4986,45 +4979,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126290861</v>
+        <v>126290647</v>
       </c>
       <c r="B41" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585819</v>
+        <v>585702</v>
       </c>
       <c r="R41" t="n">
-        <v>7068495</v>
+        <v>7068400</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5056,7 +5053,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,7 +5063,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,45 +5090,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126290808</v>
+        <v>126290708</v>
       </c>
       <c r="B42" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585766</v>
+        <v>585732</v>
       </c>
       <c r="R42" t="n">
-        <v>7068452</v>
+        <v>7068429</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5169,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5179,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,57 +5194,61 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126291855</v>
+        <v>126292441</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585640</v>
+        <v>585552</v>
       </c>
       <c r="R43" t="n">
-        <v>7068678</v>
+        <v>7068713</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,7 +5280,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5280,7 +5290,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,10 +5317,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126290386</v>
+        <v>126293117</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,7 +5347,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5346,10 +5356,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585690</v>
+        <v>585398</v>
       </c>
       <c r="R44" t="n">
-        <v>7068359</v>
+        <v>7068685</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5381,7 +5391,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5401,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126289622</v>
+        <v>126290808</v>
       </c>
       <c r="B45" t="n">
-        <v>92535</v>
+        <v>99140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,21 +5439,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5453,10 +5463,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585561</v>
+        <v>585766</v>
       </c>
       <c r="R45" t="n">
-        <v>7068428</v>
+        <v>7068452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,7 +5498,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5498,7 +5508,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5513,44 +5523,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126291922</v>
+        <v>126290861</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5570,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585613</v>
+        <v>585819</v>
       </c>
       <c r="R46" t="n">
-        <v>7068689</v>
+        <v>7068495</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,7 +5605,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5605,7 +5615,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5632,45 +5642,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126292907</v>
+        <v>126291363</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Ång</t>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585355</v>
+        <v>585786</v>
       </c>
       <c r="R47" t="n">
-        <v>7068706</v>
+        <v>7068528</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5702,7 +5712,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5712,7 +5722,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5736,6 +5746,337 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126291427</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>585743</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7068559</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126292404</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>585557</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7068699</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126292436</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Illflobäcken, Illflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>585554</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7068705</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27590-2025 artfynd.xlsx
+++ b/artfynd/A 27590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290275</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290462</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292586</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290751</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126291209</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126291293</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292486</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292399</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289622</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289597</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289640</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290184</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,6 +2478,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290250</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2505,6 +2590,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290817</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126291855</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2719,6 +2814,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126291922</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2826,6 +2926,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292374</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2933,6 +3038,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292504</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3040,6 +3150,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292842</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3147,6 +3262,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292907</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3254,6 +3374,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290723</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3361,6 +3486,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292425</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3473,6 +3603,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289969</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3590,6 +3725,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290050</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290096</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3824,6 +3969,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290158</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3941,6 +4091,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290209</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4058,6 +4213,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290524</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4175,6 +4335,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290909</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4292,6 +4457,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290936</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4409,6 +4579,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292086</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4526,6 +4701,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292757</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4638,6 +4818,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290181</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4749,6 +4934,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289885</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4860,6 +5050,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290386</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4976,6 +5171,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290592</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5087,6 +5287,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290647</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5203,6 +5408,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290708</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5314,6 +5524,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292441</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5425,6 +5640,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126293117</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5532,6 +5752,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290808</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5639,6 +5864,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126290861</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5746,6 +5976,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126291363</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5853,6 +6088,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126291427</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5960,6 +6200,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292404</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6077,8 +6322,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126292436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>